--- a/MainTop/1.06.2026 Макс Имена общее/print_sorted.xlsx
+++ b/MainTop/1.06.2026 Макс Имена общее/print_sorted.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\1.06.2026 Макс Имена общее\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C06BD09-C825-4DDA-AE41-DD0AAFFBCD64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9900EC-5048-4C3A-B829-EAC8DAC47FDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -815,7 +815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S113"/>
+  <dimension ref="A1:S114"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.42578125" customWidth="1"/>
@@ -7492,6 +7492,44 @@
         <v>0</v>
       </c>
     </row>
+    <row r="114" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="F114">
+        <f>SUM(F2:F113)</f>
+        <v>205</v>
+      </c>
+      <c r="G114">
+        <f t="shared" ref="G114:M114" si="0">SUM(G2:G113)</f>
+        <v>205</v>
+      </c>
+      <c r="H114">
+        <f t="shared" si="0"/>
+        <v>198</v>
+      </c>
+      <c r="I114">
+        <f t="shared" si="0"/>
+        <v>198</v>
+      </c>
+      <c r="J114">
+        <f t="shared" si="0"/>
+        <v>173</v>
+      </c>
+      <c r="K114">
+        <f t="shared" si="0"/>
+        <v>173</v>
+      </c>
+      <c r="L114">
+        <f t="shared" si="0"/>
+        <v>151</v>
+      </c>
+      <c r="M114">
+        <f t="shared" si="0"/>
+        <v>151</v>
+      </c>
+      <c r="N114">
+        <f>SUM(N2:N113)</f>
+        <v>138</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/MainTop/1.06.2026 Макс Имена общее/print_sorted.xlsx
+++ b/MainTop/1.06.2026 Макс Имена общее/print_sorted.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\1.06.2026 Макс Имена общее\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9900EC-5048-4C3A-B829-EAC8DAC47FDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E83DA89-1AAD-400F-9605-5A4A8CB76154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -815,14 +815,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S114"/>
+  <dimension ref="A1:T114"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.42578125" customWidth="1"/>
     <col min="2" max="2" width="0" hidden="1" customWidth="1"/>
     <col min="3" max="4" width="9.140625" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="5" customWidth="1"/>
-    <col min="6" max="19" width="4.5703125" customWidth="1"/>
+    <col min="6" max="18" width="4.5703125" customWidth="1"/>
+    <col min="19" max="19" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -7433,7 +7434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>130</v>
       </c>
@@ -7492,7 +7493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:20" x14ac:dyDescent="0.25">
       <c r="F114">
         <f>SUM(F2:F113)</f>
         <v>205</v>
@@ -7528,6 +7529,30 @@
       <c r="N114">
         <f>SUM(N2:N113)</f>
         <v>138</v>
+      </c>
+      <c r="O114">
+        <f t="shared" ref="O114:R114" si="1">SUM(O2:O113)</f>
+        <v>138</v>
+      </c>
+      <c r="P114">
+        <f t="shared" si="1"/>
+        <v>132</v>
+      </c>
+      <c r="Q114">
+        <f t="shared" si="1"/>
+        <v>132</v>
+      </c>
+      <c r="R114">
+        <f t="shared" si="1"/>
+        <v>110</v>
+      </c>
+      <c r="S114">
+        <f>SUM(S2:S113)</f>
+        <v>110</v>
+      </c>
+      <c r="T114">
+        <f>SUM(F114:S114)</f>
+        <v>2214</v>
       </c>
     </row>
   </sheetData>
